--- a/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_star.xlsx
+++ b/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_star.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\Poincare beams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEAAF118-4B56-4233-8D5C-C1AC1D1B1DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACA3673-AA45-4414-9C30-D4183601B5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10980" yWindow="945" windowWidth="12630" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12975" yWindow="1500" windowWidth="13350" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -478,7 +478,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>33.991999999999997</v>
+        <v>34.612000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -492,7 +492,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1">
-        <v>12.612</v>
+        <v>12.573</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -576,7 +576,8 @@
         <v>8</v>
       </c>
       <c r="D11" s="1">
-        <v>0.56000000000000005</v>
+        <f>D41*0.8</f>
+        <v>0.76</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -680,7 +681,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>33.991999999999997</v>
+        <v>34.612000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -694,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>12.612</v>
+        <v>12.573</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -778,7 +779,8 @@
         <v>8</v>
       </c>
       <c r="D26" s="1">
-        <v>0.56000000000000005</v>
+        <f>D41*0.8</f>
+        <v>0.76</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -882,7 +884,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="1">
-        <v>33.991999999999997</v>
+        <v>34.612000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -896,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="1">
-        <v>12.612</v>
+        <v>12.573</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -980,7 +982,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="1">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1078,7 +1080,7 @@
         <v>3</v>
       </c>
       <c r="D49" s="2">
-        <v>33.932000000000002</v>
+        <v>34.612000000000002</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1092,7 +1094,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="2">
-        <v>12.611000000000001</v>
+        <v>12.573</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1135,7 +1137,7 @@
       </c>
       <c r="D53" s="2">
         <f>D83+50</f>
-        <v>84.2</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1282,7 +1284,7 @@
         <v>3</v>
       </c>
       <c r="D64" s="2">
-        <v>33.932000000000002</v>
+        <v>34.612000000000002</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1296,7 +1298,7 @@
         <v>4</v>
       </c>
       <c r="D65" s="2">
-        <v>12.611000000000001</v>
+        <v>12.573</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,7 +1341,7 @@
       </c>
       <c r="D68" s="2">
         <f>D83-25</f>
-        <v>9.2000000000000028</v>
+        <v>3.2000000000000028</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1486,7 +1488,7 @@
         <v>3</v>
       </c>
       <c r="D79" s="2">
-        <v>33.932000000000002</v>
+        <v>34.612000000000002</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1500,7 +1502,7 @@
         <v>4</v>
       </c>
       <c r="D80" s="2">
-        <v>12.611000000000001</v>
+        <v>12.573</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1542,8 +1544,8 @@
         <v>6</v>
       </c>
       <c r="D83" s="2">
-        <f>100-65.8</f>
-        <v>34.200000000000003</v>
+        <f>100-71.8</f>
+        <v>28.200000000000003</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -1585,7 +1587,7 @@
         <v>8</v>
       </c>
       <c r="D86" s="2">
-        <v>1.08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">

--- a/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_star.xlsx
+++ b/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_star.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\Poincare beams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACA3673-AA45-4414-9C30-D4183601B5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C646375-1581-4321-B0B1-C7D242895FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12975" yWindow="1500" windowWidth="13350" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -478,7 +478,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>34.612000000000002</v>
+        <v>34.752000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -492,7 +492,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1">
-        <v>12.573</v>
+        <v>12.574</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -681,7 +681,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>34.612000000000002</v>
+        <v>34.752000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>12.573</v>
+        <v>12.574</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -884,7 +884,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="1">
-        <v>34.612000000000002</v>
+        <v>34.752000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -898,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="1">
-        <v>12.573</v>
+        <v>12.574</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1079,8 +1079,8 @@
       <c r="C49" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D49" s="2">
-        <v>34.612000000000002</v>
+      <c r="D49" s="1">
+        <v>34.752000000000002</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1093,8 +1093,8 @@
       <c r="C50" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D50" s="2">
-        <v>12.573</v>
+      <c r="D50" s="1">
+        <v>12.574</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D53" s="2">
         <f>D83+50</f>
-        <v>78.2</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,8 +1283,8 @@
       <c r="C64" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D64" s="2">
-        <v>34.612000000000002</v>
+      <c r="D64" s="1">
+        <v>34.752000000000002</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1297,8 +1297,8 @@
       <c r="C65" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D65" s="2">
-        <v>12.573</v>
+      <c r="D65" s="1">
+        <v>12.574</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D68" s="2">
         <f>D83-25</f>
-        <v>3.2000000000000028</v>
+        <v>11.799999999999997</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1487,8 +1487,8 @@
       <c r="C79" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D79" s="2">
-        <v>34.612000000000002</v>
+      <c r="D79" s="1">
+        <v>34.752000000000002</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1501,8 +1501,8 @@
       <c r="C80" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D80" s="2">
-        <v>12.573</v>
+      <c r="D80" s="1">
+        <v>12.574</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1544,8 +1544,8 @@
         <v>6</v>
       </c>
       <c r="D83" s="2">
-        <f>100-71.8</f>
-        <v>28.200000000000003</v>
+        <f>100-63.2</f>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">

--- a/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_star.xlsx
+++ b/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_star.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\Poincare beams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C646375-1581-4321-B0B1-C7D242895FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EB91EE-4B25-4C8E-8ECD-30EF4DA26A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12975" yWindow="1500" windowWidth="13350" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -478,7 +478,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>34.752000000000002</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -492,7 +492,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1">
-        <v>12.574</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -577,7 +577,7 @@
       </c>
       <c r="D11" s="1">
         <f>D41*0.8</f>
-        <v>0.76</v>
+        <v>0.72000000000000008</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -681,7 +681,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>34.752000000000002</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>12.574</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -780,7 +780,7 @@
       </c>
       <c r="D26" s="1">
         <f>D41*0.8</f>
-        <v>0.76</v>
+        <v>0.72000000000000008</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -884,7 +884,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="1">
-        <v>34.752000000000002</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -898,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="1">
-        <v>12.574</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -982,7 +982,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="1">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1080,7 +1080,7 @@
         <v>3</v>
       </c>
       <c r="D49" s="1">
-        <v>34.752000000000002</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1094,7 +1094,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="1">
-        <v>12.574</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D53" s="2">
         <f>D83+50</f>
-        <v>86.8</v>
+        <v>146.80000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1284,7 +1284,7 @@
         <v>3</v>
       </c>
       <c r="D64" s="1">
-        <v>34.752000000000002</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1298,7 +1298,7 @@
         <v>4</v>
       </c>
       <c r="D65" s="1">
-        <v>12.574</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D68" s="2">
         <f>D83-25</f>
-        <v>11.799999999999997</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1488,7 +1488,7 @@
         <v>3</v>
       </c>
       <c r="D79" s="1">
-        <v>34.752000000000002</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1502,7 +1502,7 @@
         <v>4</v>
       </c>
       <c r="D80" s="1">
-        <v>12.574</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1544,8 +1544,7 @@
         <v>6</v>
       </c>
       <c r="D83" s="2">
-        <f>100-63.2</f>
-        <v>36.799999999999997</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
